--- a/artfynd/A 51078-2023 artfynd.xlsx
+++ b/artfynd/A 51078-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51078-2023 artfynd.xlsx
+++ b/artfynd/A 51078-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99431569</v>
+        <v>99431561</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,21 +710,17 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Träthult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566590.024363736</v>
+        <v>566590</v>
       </c>
       <c r="R2" t="n">
-        <v>6359432.540871517</v>
+        <v>6359432</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -798,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99431561</v>
+        <v>99431557</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,16 +800,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100090</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -845,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566590.024363736</v>
+        <v>566590</v>
       </c>
       <c r="R3" t="n">
-        <v>6359432.540871517</v>
+        <v>6359432</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -914,6 +900,234 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>99431359</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Träthult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566590</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6359432</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-03-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-03-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99431569</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Träthult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566590</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6359432</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-03-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-03-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51078-2023 artfynd.xlsx
+++ b/artfynd/A 51078-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99431561</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99431557</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99431359</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,8 +1148,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99431569</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>